--- a/Daily_Progress_Report.xlsx
+++ b/Daily_Progress_Report.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\Daily_Progress\daily-progress-tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="53">
   <si>
     <t>Date</t>
   </si>
@@ -326,6 +326,12 @@
   </si>
   <si>
     <t>Lecture/Notes</t>
+  </si>
+  <si>
+    <t>21-09-2026</t>
+  </si>
+  <si>
+    <t>sql window function</t>
   </si>
 </sst>
 </file>
@@ -675,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -876,6 +882,14 @@
         <v>36</v>
       </c>
     </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" t="s">
+        <v>52</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Daily_Progress_Report.xlsx
+++ b/Daily_Progress_Report.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="59">
   <si>
     <t>Date</t>
   </si>
@@ -331,7 +331,38 @@
     <t>21-09-2026</t>
   </si>
   <si>
-    <t>sql window function</t>
+    <t>LSTM + Longest Increasing Subsequence (LIS)</t>
+  </si>
+  <si>
+    <t>LSTM notes/lecture + LeetCode</t>
+  </si>
+  <si>
+    <t>Studied LSTM in more depth, focusing on how the Forget Gate, Input Gate, Cell State and Output Gate work together to control information flow and handle long-term dependencies. Also explored the Dynamic Programming approach for LIS</t>
+  </si>
+  <si>
+    <t>Strengthened understanding of LSTM architecture, gates and cell state. Improved understanding of sequence modeling and DP-based problem solving.</t>
+  </si>
+  <si>
+    <t>LSTM gate mechanism and information flow; LIS example using DP</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Solved </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LeetCode – Longest Increasing Subsequence</t>
+    </r>
+  </si>
+  <si>
+    <t>Need further practice with LSTM equations and Dynamic Programming patterns.</t>
   </si>
 </sst>
 </file>
@@ -882,12 +913,33 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="144" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="3" t="s">
         <v>52</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Daily_Progress_Report.xlsx
+++ b/Daily_Progress_Report.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="74">
   <si>
     <t>Date</t>
   </si>
@@ -363,6 +363,74 @@
   </si>
   <si>
     <t>Need further practice with LSTM equations and Dynamic Programming patterns.</t>
+  </si>
+  <si>
+    <t>22-09-2026</t>
+  </si>
+  <si>
+    <t>23-09-2026</t>
+  </si>
+  <si>
+    <t>LSTM Notes / Lecture</t>
+  </si>
+  <si>
+    <t>LSTM — Deep Dive</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">studied the LSTM architecture in greater depth, focusing on how the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Forget Gate, Input Gate, Cell State, and Output Gate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> work together to control information flow and handle long-term dependencies.</t>
+    </r>
+  </si>
+  <si>
+    <t>Strengthened understanding of LSTM architecture, gate mechanisms, cell state, and sequence modeling.</t>
+  </si>
+  <si>
+    <t>Worked through LSTM gate equations and information-flow examples.</t>
+  </si>
+  <si>
+    <t>Revise LSTM architecture and practice gate equations.</t>
+  </si>
+  <si>
+    <t>Encoder–Decoder Architecture</t>
+  </si>
+  <si>
+    <t>Started learning the Encoder–Decoder architecture and understood the basic idea of how an input sequence is encoded into a representation and then decoded to generate an output sequence.</t>
+  </si>
+  <si>
+    <t>Understood the basic working of Encoder and Decoder and their role in sequence-to-sequence (Seq2Seq) tasks.</t>
+  </si>
+  <si>
+    <t>Basic sequence-to-sequence example such as language translation.</t>
+  </si>
+  <si>
+    <t>Need to understand the Encoder–Decoder flow and its connection with Attention in more depth.</t>
+  </si>
+  <si>
+    <t>Study Encoder–Decoder architecture in detail and start Attention Mechanism.</t>
+  </si>
+  <si>
+    <t>In Progress</t>
   </si>
 </sst>
 </file>
@@ -712,7 +780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -942,6 +1010,68 @@
         <v>18</v>
       </c>
     </row>
+    <row r="8" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Daily_Progress_Report.xlsx
+++ b/Daily_Progress_Report.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="96">
   <si>
     <t>Date</t>
   </si>
@@ -431,6 +431,229 @@
   </si>
   <si>
     <t>In Progress</t>
+  </si>
+  <si>
+    <t>24-09-2026</t>
+  </si>
+  <si>
+    <t>Encoder–Decoder — Working &amp; Limitations</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Studied the detailed working of the Encoder–Decoder architecture, including </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Teacher Forcing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Bottleneck Problem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in sequence-to-sequence models.</t>
+    </r>
+  </si>
+  <si>
+    <t>Understood how the encoder processes the input sequence, how the decoder generates the output step-by-step, and how Teacher Forcing helps during training. Also understood why the fixed-length context vector creates a bottleneck for long sequences.</t>
+  </si>
+  <si>
+    <t>Worked through a basic sequence-to-sequence translation example using Encoder and Decoder.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Need to understand how </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Attention Mechanism</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> solves the bottleneck problem.</t>
+    </r>
+  </si>
+  <si>
+    <t>Study Attention Mechanism and how it improves Encoder–Decoder models.</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>25-09-2026</t>
+  </si>
+  <si>
+    <t>Attention Mechanism</t>
+  </si>
+  <si>
+    <t>Studied the Attention Mechanism and understood how it allows the decoder to focus on the most relevant parts of the input sequence while generating each output token.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Understood the need for Attention, how attention weights are calculated, and how </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Query, Key, and Value</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> concepts help determine relevant information.</t>
+    </r>
+  </si>
+  <si>
+    <t>Worked through a simple attention example and analyzed how different input words receive different attention weights.</t>
+  </si>
+  <si>
+    <t>Need more practice with attention score calculations and the complete Attention workflow.</t>
+  </si>
+  <si>
+    <t>Revise Attention Mechanism and study its mathematical calculations in detail.</t>
+  </si>
+  <si>
+    <t>26-09-2026</t>
+  </si>
+  <si>
+    <t>Bahdanau &amp; Luong Attention</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Studied </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Bahdanau (Additive) Attention</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Luong (Multiplicative) Attention</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, focusing on how both approaches calculate attention scores and help the decoder focus on relevant encoder states.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Understood the working of both attention mechanisms and the key difference between </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>additive and multiplicative attention</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Worked through attention score calculations and compared Bahdanau and Luong attention.</t>
+  </si>
+  <si>
+    <t>Need more practice with the mathematical calculations and implementation of both attention mechanisms.</t>
+  </si>
+  <si>
+    <t>Revise Bahdanau and Luong Attention and study their implementation.</t>
   </si>
 </sst>
 </file>
@@ -780,7 +1003,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -1065,12 +1288,92 @@
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
+    <row r="10" spans="1:10" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="144" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>95</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
